--- a/HNG_2/HNG/HNGK_HNGH_Gastric_DHYHN_Dr_Dung.xlsx
+++ b/HNG_2/HNG/HNGK_HNGH_Gastric_DHYHN_Dr_Dung.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VoDacHo\Gastric\HNG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\XN\du-an-dung-chung\HNG_2\HNG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEF98D09-AE4B-4AB8-8EAE-A4285EC241A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7515" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Thông tin lâm sàng" sheetId="3" r:id="rId1"/>
@@ -20,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">HNGK!$A$1:$T$107</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,22 +40,31 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>tc={36EBFC15-0B97-40E5-B7DD-21EF945088B3}</author>
     <author>DAM THI MY HUYEN</author>
     <author>tc={34FF9781-DD42-9A48-A076-FADE82BA2D88}</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{36EBFC15-0B97-40E5-B7DD-21EF945088B3}">
+    <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     @NGUYEN VAN THIEN CHI @TRAN THI TRANG @VO TRUONG DANG HUY Gửi mọi người file quản lý mẫu ung thư dạ dày bác sĩ Dung, đại học y Hà Nội.</t>
+        </r>
       </text>
     </comment>
-    <comment ref="K96" authorId="1" shapeId="0" xr:uid="{7BE65AFB-2A68-4088-B7A7-9AF07B0B802B}">
+    <comment ref="K96" authorId="1" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -71,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K97" authorId="1" shapeId="0" xr:uid="{5C7A0A3A-59BC-4537-B00E-624DCAD4C6D1}">
+    <comment ref="K97" authorId="1" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -86,12 +94,21 @@
         </r>
       </text>
     </comment>
-    <comment ref="K100" authorId="2" shapeId="0" xr:uid="{34FF9781-DD42-9A48-A076-FADE82BA2D88}">
+    <comment ref="K100" authorId="2" shapeId="0">
       <text>
-        <t xml:space="preserve">[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     có cục máu đông </t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -2453,8 +2470,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3076,7 +3093,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
+    <cellStyle name="Hyperlink" xfId="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -3434,51 +3451,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DC4403F-26C6-49DC-B3F1-DDBAEABF7996}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="103" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1" location="gid=0" xr:uid="{6A5FE549-2043-4ED9-ADEA-1C0693A38EAE}"/>
+    <hyperlink ref="A1" r:id="rId1" location="gid=0"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T107"/>
-  <sheetFormatPr defaultColWidth="9.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" style="8"/>
-    <col min="2" max="2" width="17.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="12.5703125" style="8" customWidth="1"/>
+    <col min="1" max="1" width="9.375" style="8"/>
+    <col min="2" max="2" width="17.875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="12.625" style="8" customWidth="1"/>
     <col min="7" max="7" width="22" style="8" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" style="8" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" style="8" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.42578125" style="8"/>
-    <col min="12" max="12" width="29.85546875" style="8" customWidth="1"/>
-    <col min="13" max="13" width="32.28515625" style="97" customWidth="1"/>
-    <col min="14" max="14" width="19.5703125" style="8" customWidth="1"/>
-    <col min="15" max="15" width="17.28515625" style="8" customWidth="1"/>
-    <col min="16" max="16" width="19.5703125" style="8" customWidth="1"/>
-    <col min="17" max="19" width="9.42578125" style="8"/>
-    <col min="20" max="20" width="41.42578125" style="8" customWidth="1"/>
-    <col min="21" max="16384" width="9.42578125" style="8"/>
+    <col min="8" max="8" width="14.125" style="8" customWidth="1"/>
+    <col min="9" max="9" width="13.25" style="8" customWidth="1"/>
+    <col min="10" max="10" width="12.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.375" style="8"/>
+    <col min="12" max="12" width="29.875" style="8" customWidth="1"/>
+    <col min="13" max="13" width="32.25" style="97" customWidth="1"/>
+    <col min="14" max="14" width="19.625" style="8" customWidth="1"/>
+    <col min="15" max="15" width="17.25" style="8" customWidth="1"/>
+    <col min="16" max="16" width="19.625" style="8" customWidth="1"/>
+    <col min="17" max="19" width="9.375" style="8"/>
+    <col min="20" max="20" width="41.375" style="8" customWidth="1"/>
+    <col min="21" max="16384" width="9.375" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="32" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" s="32" customFormat="1" ht="30">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -3540,7 +3556,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="45">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -3592,7 +3608,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20">
       <c r="A3" s="10">
         <v>2</v>
       </c>
@@ -3643,7 +3659,7 @@
       <c r="S3" s="10"/>
       <c r="T3" s="10"/>
     </row>
-    <row r="4" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -3694,7 +3710,7 @@
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
     </row>
-    <row r="5" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -3745,7 +3761,7 @@
       <c r="S5" s="3"/>
       <c r="T5" s="3"/>
     </row>
-    <row r="6" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -3796,7 +3812,7 @@
       <c r="S6" s="3"/>
       <c r="T6" s="3"/>
     </row>
-    <row r="7" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20">
       <c r="A7" s="10">
         <v>6</v>
       </c>
@@ -3847,7 +3863,7 @@
       <c r="S7" s="10"/>
       <c r="T7" s="10"/>
     </row>
-    <row r="8" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -3900,7 +3916,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -3953,7 +3969,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -4004,7 +4020,7 @@
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
     </row>
-    <row r="11" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -4055,7 +4071,7 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
     </row>
-    <row r="12" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -4106,7 +4122,7 @@
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
     </row>
-    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -4159,7 +4175,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -4210,7 +4226,7 @@
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
     </row>
-    <row r="15" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20">
       <c r="A15" s="10">
         <v>14</v>
       </c>
@@ -4261,7 +4277,7 @@
       <c r="S15" s="10"/>
       <c r="T15" s="10"/>
     </row>
-    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -4312,7 +4328,7 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
     </row>
-    <row r="17" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -4363,7 +4379,7 @@
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
     </row>
-    <row r="18" spans="1:20" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" ht="60">
       <c r="A18" s="10">
         <v>17</v>
       </c>
@@ -4414,7 +4430,7 @@
       <c r="S18" s="10"/>
       <c r="T18" s="10"/>
     </row>
-    <row r="19" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -4465,7 +4481,7 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
     </row>
-    <row r="20" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -4516,7 +4532,7 @@
       <c r="S20" s="3"/>
       <c r="T20" s="3"/>
     </row>
-    <row r="21" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20">
       <c r="A21" s="10">
         <v>20</v>
       </c>
@@ -4567,7 +4583,7 @@
       <c r="S21" s="10"/>
       <c r="T21" s="10"/>
     </row>
-    <row r="22" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -4618,7 +4634,7 @@
       <c r="S22" s="3"/>
       <c r="T22" s="3"/>
     </row>
-    <row r="23" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -4669,7 +4685,7 @@
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
     </row>
-    <row r="24" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20">
       <c r="A24" s="10">
         <v>23</v>
       </c>
@@ -4720,7 +4736,7 @@
       <c r="S24" s="10"/>
       <c r="T24" s="10"/>
     </row>
-    <row r="25" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -4771,7 +4787,7 @@
       <c r="S25" s="3"/>
       <c r="T25" s="3"/>
     </row>
-    <row r="26" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -4822,7 +4838,7 @@
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
     </row>
-    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -4875,7 +4891,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="28" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -4926,7 +4942,7 @@
       <c r="S28" s="3"/>
       <c r="T28" s="3"/>
     </row>
-    <row r="29" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -4977,7 +4993,7 @@
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
     </row>
-    <row r="30" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -5030,7 +5046,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="31" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -5081,7 +5097,7 @@
       <c r="S31" s="3"/>
       <c r="T31" s="3"/>
     </row>
-    <row r="32" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -5132,7 +5148,7 @@
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
     </row>
-    <row r="33" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -5183,7 +5199,7 @@
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
     </row>
-    <row r="34" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -5234,7 +5250,7 @@
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
     </row>
-    <row r="35" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -5285,7 +5301,7 @@
       <c r="S35" s="3"/>
       <c r="T35" s="3"/>
     </row>
-    <row r="36" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20">
       <c r="A36" s="7">
         <v>35</v>
       </c>
@@ -5336,7 +5352,7 @@
       <c r="S36" s="7"/>
       <c r="T36" s="7"/>
     </row>
-    <row r="37" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20">
       <c r="A37" s="50">
         <v>36</v>
       </c>
@@ -5389,7 +5405,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20">
       <c r="A38" s="50">
         <v>37</v>
       </c>
@@ -5442,7 +5458,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="39" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20">
       <c r="A39" s="57">
         <v>38</v>
       </c>
@@ -5495,7 +5511,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="40" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20">
       <c r="A40" s="20">
         <v>39</v>
       </c>
@@ -5548,7 +5564,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="41" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20">
       <c r="A41" s="50">
         <v>40</v>
       </c>
@@ -5601,7 +5617,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="42" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20">
       <c r="A42" s="50">
         <v>41</v>
       </c>
@@ -5652,7 +5668,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20">
       <c r="A43" s="57">
         <v>42</v>
       </c>
@@ -5701,7 +5717,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="44" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20">
       <c r="A44" s="61">
         <v>43</v>
       </c>
@@ -5752,7 +5768,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="45" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20">
       <c r="A45" s="62">
         <v>44</v>
       </c>
@@ -5803,7 +5819,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="46" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20">
       <c r="A46" s="50">
         <v>45</v>
       </c>
@@ -5856,7 +5872,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="47" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20">
       <c r="A47" s="50">
         <v>46</v>
       </c>
@@ -5907,7 +5923,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="48" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20">
       <c r="A48" s="64">
         <v>47</v>
       </c>
@@ -5960,7 +5976,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="49" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" ht="30">
       <c r="A49" s="55">
         <v>48</v>
       </c>
@@ -6011,7 +6027,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="50" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20">
       <c r="A50" s="34">
         <v>49</v>
       </c>
@@ -6062,7 +6078,7 @@
       <c r="S50" s="33"/>
       <c r="T50" s="33"/>
     </row>
-    <row r="51" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20">
       <c r="A51" s="28">
         <v>50</v>
       </c>
@@ -6113,7 +6129,7 @@
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
     </row>
-    <row r="52" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20">
       <c r="A52" s="55">
         <v>51</v>
       </c>
@@ -6164,7 +6180,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="53" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20">
       <c r="A53" s="55">
         <v>52</v>
       </c>
@@ -6215,7 +6231,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="54" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20">
       <c r="A54" s="55">
         <v>53</v>
       </c>
@@ -6268,7 +6284,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="55" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20">
       <c r="A55" s="55">
         <v>54</v>
       </c>
@@ -6321,7 +6337,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="56" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20">
       <c r="A56" s="55">
         <v>55</v>
       </c>
@@ -6374,7 +6390,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="57" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20">
       <c r="A57" s="28">
         <v>56</v>
       </c>
@@ -6425,7 +6441,7 @@
       <c r="S57" s="3"/>
       <c r="T57" s="3"/>
     </row>
-    <row r="58" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20">
       <c r="A58" s="55">
         <v>57</v>
       </c>
@@ -6478,7 +6494,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="59" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20">
       <c r="A59" s="55">
         <v>58</v>
       </c>
@@ -6531,7 +6547,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="60" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20">
       <c r="A60" s="55">
         <v>59</v>
       </c>
@@ -6584,7 +6600,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="61" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20">
       <c r="A61" s="55">
         <v>60</v>
       </c>
@@ -6637,7 +6653,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="62" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20">
       <c r="A62" s="55">
         <v>61</v>
       </c>
@@ -6690,7 +6706,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="63" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20">
       <c r="A63" s="55">
         <v>62</v>
       </c>
@@ -6743,7 +6759,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="64" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20">
       <c r="A64" s="55">
         <v>63</v>
       </c>
@@ -6796,7 +6812,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="65" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20">
       <c r="A65" s="55">
         <v>64</v>
       </c>
@@ -6849,7 +6865,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="66" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:20">
       <c r="A66" s="55">
         <v>65</v>
       </c>
@@ -6902,7 +6918,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:20">
       <c r="A67" s="55">
         <v>66</v>
       </c>
@@ -6953,7 +6969,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="68" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:20">
       <c r="A68" s="55">
         <v>67</v>
       </c>
@@ -7004,7 +7020,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="69" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:20">
       <c r="A69" s="55">
         <v>68</v>
       </c>
@@ -7055,7 +7071,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="70" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:20">
       <c r="A70" s="28">
         <v>69</v>
       </c>
@@ -7104,7 +7120,7 @@
       <c r="S70" s="3"/>
       <c r="T70" s="3"/>
     </row>
-    <row r="71" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20">
       <c r="A71" s="55">
         <v>70</v>
       </c>
@@ -7157,7 +7173,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="72" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20">
       <c r="A72" s="25">
         <v>71</v>
       </c>
@@ -7207,7 +7223,7 @@
       <c r="S72" s="7"/>
       <c r="T72" s="7"/>
     </row>
-    <row r="73" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20">
       <c r="A73" s="3">
         <v>72</v>
       </c>
@@ -7258,7 +7274,7 @@
       <c r="S73" s="3"/>
       <c r="T73" s="3"/>
     </row>
-    <row r="74" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20">
       <c r="A74" s="67">
         <v>73</v>
       </c>
@@ -7309,7 +7325,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="75" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:20">
       <c r="A75" s="3">
         <v>74</v>
       </c>
@@ -7360,7 +7376,7 @@
       <c r="S75" s="7"/>
       <c r="T75" s="7"/>
     </row>
-    <row r="76" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:20">
       <c r="A76" s="3">
         <v>75</v>
       </c>
@@ -7411,7 +7427,7 @@
       <c r="S76" s="7"/>
       <c r="T76" s="7"/>
     </row>
-    <row r="77" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:20">
       <c r="A77" s="28">
         <v>76</v>
       </c>
@@ -7462,7 +7478,7 @@
       <c r="S77" s="7"/>
       <c r="T77" s="7"/>
     </row>
-    <row r="78" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:20">
       <c r="A78" s="28">
         <v>77</v>
       </c>
@@ -7513,7 +7529,7 @@
       <c r="S78" s="3"/>
       <c r="T78" s="3"/>
     </row>
-    <row r="79" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:20">
       <c r="A79" s="28">
         <v>78</v>
       </c>
@@ -7564,7 +7580,7 @@
       <c r="S79" s="3"/>
       <c r="T79" s="3"/>
     </row>
-    <row r="80" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:20">
       <c r="A80" s="28">
         <v>79</v>
       </c>
@@ -7615,7 +7631,7 @@
       <c r="S80" s="3"/>
       <c r="T80" s="3"/>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20">
       <c r="A81" s="28">
         <v>80</v>
       </c>
@@ -7664,7 +7680,7 @@
       <c r="S81" s="3"/>
       <c r="T81" s="3"/>
     </row>
-    <row r="82" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20">
       <c r="A82" s="28">
         <v>81</v>
       </c>
@@ -7713,7 +7729,7 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
     </row>
-    <row r="83" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20">
       <c r="A83" s="28">
         <v>82</v>
       </c>
@@ -7762,7 +7778,7 @@
       <c r="S83" s="3"/>
       <c r="T83" s="3"/>
     </row>
-    <row r="84" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20">
       <c r="A84" s="28">
         <v>83</v>
       </c>
@@ -7811,7 +7827,7 @@
       <c r="S84" s="3"/>
       <c r="T84" s="3"/>
     </row>
-    <row r="85" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20">
       <c r="A85" s="28">
         <v>84</v>
       </c>
@@ -7860,7 +7876,7 @@
       <c r="S85" s="3"/>
       <c r="T85" s="3"/>
     </row>
-    <row r="86" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20">
       <c r="A86" s="28">
         <v>85</v>
       </c>
@@ -7911,7 +7927,7 @@
       <c r="S86" s="3"/>
       <c r="T86" s="3"/>
     </row>
-    <row r="87" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20">
       <c r="A87" s="28">
         <v>86</v>
       </c>
@@ -7962,7 +7978,7 @@
       <c r="S87" s="7"/>
       <c r="T87" s="7"/>
     </row>
-    <row r="88" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20">
       <c r="A88" s="28">
         <v>87</v>
       </c>
@@ -8013,7 +8029,7 @@
       <c r="S88" s="3"/>
       <c r="T88" s="3"/>
     </row>
-    <row r="89" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20">
       <c r="A89" s="28">
         <v>88</v>
       </c>
@@ -8062,7 +8078,7 @@
       <c r="S89" s="3"/>
       <c r="T89" s="3"/>
     </row>
-    <row r="90" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20">
       <c r="A90" s="28">
         <v>89</v>
       </c>
@@ -8113,7 +8129,7 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
     </row>
-    <row r="91" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20">
       <c r="A91" s="28">
         <v>90</v>
       </c>
@@ -8160,7 +8176,7 @@
       <c r="S91" s="3"/>
       <c r="T91" s="3"/>
     </row>
-    <row r="92" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20">
       <c r="A92" s="28">
         <v>91</v>
       </c>
@@ -8209,7 +8225,7 @@
       <c r="S92" s="7"/>
       <c r="T92" s="7"/>
     </row>
-    <row r="93" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20">
       <c r="A93" s="28">
         <v>92</v>
       </c>
@@ -8259,7 +8275,7 @@
       <c r="S93" s="3"/>
       <c r="T93" s="3"/>
     </row>
-    <row r="94" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20">
       <c r="A94" s="28">
         <v>93</v>
       </c>
@@ -8306,7 +8322,7 @@
       <c r="S94" s="7"/>
       <c r="T94" s="7"/>
     </row>
-    <row r="95" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20">
       <c r="A95" s="28">
         <v>94</v>
       </c>
@@ -8357,7 +8373,7 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
     </row>
-    <row r="96" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20">
       <c r="A96" s="28">
         <f>A95+1</f>
         <v>95</v>
@@ -8405,7 +8421,7 @@
       <c r="S96" s="7"/>
       <c r="T96" s="3"/>
     </row>
-    <row r="97" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20">
       <c r="A97" s="28">
         <f t="shared" ref="A97:A102" si="5">A96+1</f>
         <v>96</v>
@@ -8457,7 +8473,7 @@
       <c r="S97" s="3"/>
       <c r="T97" s="12"/>
     </row>
-    <row r="98" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20">
       <c r="A98" s="28">
         <f t="shared" si="5"/>
         <v>97</v>
@@ -8507,7 +8523,7 @@
       <c r="S98" s="82"/>
       <c r="T98" s="3"/>
     </row>
-    <row r="99" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20">
       <c r="A99" s="28">
         <f t="shared" si="5"/>
         <v>98</v>
@@ -8557,7 +8573,7 @@
       <c r="S99" s="7"/>
       <c r="T99" s="3"/>
     </row>
-    <row r="100" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20">
       <c r="A100" s="28">
         <f t="shared" si="5"/>
         <v>99</v>
@@ -8605,7 +8621,7 @@
       <c r="S100" s="3"/>
       <c r="T100" s="12"/>
     </row>
-    <row r="101" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20">
       <c r="A101" s="28">
         <f t="shared" si="5"/>
         <v>100</v>
@@ -8657,7 +8673,7 @@
       <c r="S101" s="3"/>
       <c r="T101" s="13"/>
     </row>
-    <row r="102" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20">
       <c r="A102" s="28">
         <f t="shared" si="5"/>
         <v>101</v>
@@ -8705,7 +8721,7 @@
       <c r="S102" s="3"/>
       <c r="T102" s="12"/>
     </row>
-    <row r="103" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20">
       <c r="A103" s="28">
         <f>A102+1</f>
         <v>102</v>
@@ -8753,7 +8769,7 @@
       <c r="S103" s="99"/>
       <c r="T103" s="7"/>
     </row>
-    <row r="104" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20">
       <c r="A104" s="25">
         <f>A103+1</f>
         <v>103</v>
@@ -8801,7 +8817,7 @@
       <c r="S104" s="3"/>
       <c r="T104" s="3"/>
     </row>
-    <row r="105" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20">
       <c r="A105" s="3">
         <f>A104+1</f>
         <v>104</v>
@@ -8849,7 +8865,7 @@
       <c r="S105" s="3"/>
       <c r="T105" s="3"/>
     </row>
-    <row r="106" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20">
       <c r="A106" s="3">
         <f>A105+1</f>
         <v>105</v>
@@ -8897,7 +8913,7 @@
       <c r="S106" s="3"/>
       <c r="T106" s="3"/>
     </row>
-    <row r="107" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20">
       <c r="A107" s="3">
         <f>A106+1</f>
         <v>106</v>
@@ -8942,37 +8958,30 @@
       <c r="T107" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T107" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="12">
-      <filters>
-        <filter val="Kết hợp K đại tràng"/>
-        <filter val="Không mổ→Loại"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:T107"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31A1BCE7-CC55-4B23-B39A-57837C9FFB1D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T77"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
-    <col min="2" max="2" width="9.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="11.42578125" style="8" customWidth="1"/>
-    <col min="7" max="7" width="22.5703125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="9.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="11.375" style="8" customWidth="1"/>
+    <col min="7" max="7" width="22.625" style="8" customWidth="1"/>
     <col min="8" max="10" width="9" style="8"/>
-    <col min="11" max="11" width="11.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="9.42578125" style="8"/>
+    <col min="11" max="11" width="11.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="9.375" style="8"/>
     <col min="14" max="19" width="9" style="8"/>
-    <col min="20" max="20" width="39.85546875" style="8" customWidth="1"/>
+    <col min="20" max="20" width="39.875" style="8" customWidth="1"/>
     <col min="21" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="45">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -9034,7 +9043,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -9079,7 +9088,7 @@
       <c r="S2" s="3"/>
       <c r="T2" s="3"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -9126,7 +9135,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -9171,7 +9180,7 @@
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -9218,7 +9227,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -9263,7 +9272,7 @@
       <c r="S6" s="3"/>
       <c r="T6" s="3"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -9310,7 +9319,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -9355,7 +9364,7 @@
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -9402,7 +9411,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -9447,7 +9456,7 @@
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -9494,7 +9503,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -9539,7 +9548,7 @@
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -9584,7 +9593,7 @@
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -9629,7 +9638,7 @@
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -9676,7 +9685,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -9721,7 +9730,7 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -9766,7 +9775,7 @@
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -9813,7 +9822,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -9858,7 +9867,7 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -9903,7 +9912,7 @@
       <c r="S20" s="3"/>
       <c r="T20" s="3"/>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -9948,7 +9957,7 @@
       <c r="S21" s="3"/>
       <c r="T21" s="3"/>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -9993,7 +10002,7 @@
       <c r="S22" s="3"/>
       <c r="T22" s="3"/>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -10040,7 +10049,7 @@
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20">
       <c r="A24" s="7">
         <v>23</v>
       </c>
@@ -10089,7 +10098,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20">
       <c r="A25" s="7">
         <v>24</v>
       </c>
@@ -10136,7 +10145,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20">
       <c r="A26" s="45">
         <v>25</v>
       </c>
@@ -10183,7 +10192,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20">
       <c r="A27" s="22">
         <v>26</v>
       </c>
@@ -10230,7 +10239,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20">
       <c r="A28" s="22">
         <v>27</v>
       </c>
@@ -10275,7 +10284,7 @@
       <c r="S28" s="22"/>
       <c r="T28" s="22"/>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20">
       <c r="A29" s="22">
         <v>28</v>
       </c>
@@ -10320,7 +10329,7 @@
       <c r="S29" s="22"/>
       <c r="T29" s="22"/>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20">
       <c r="A30" s="22">
         <v>29</v>
       </c>
@@ -10365,7 +10374,7 @@
       <c r="S30" s="22"/>
       <c r="T30" s="22"/>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20">
       <c r="A31" s="23">
         <v>30</v>
       </c>
@@ -10410,7 +10419,7 @@
       <c r="S31" s="23"/>
       <c r="T31" s="23"/>
     </row>
-    <row r="32" spans="1:20" s="83" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" s="83" customFormat="1">
       <c r="A32" s="50">
         <v>31</v>
       </c>
@@ -10457,7 +10466,7 @@
       <c r="S32" s="50"/>
       <c r="T32" s="50"/>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -10502,7 +10511,7 @@
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -10547,7 +10556,7 @@
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
     </row>
-    <row r="35" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" ht="30">
       <c r="A35" s="36">
         <v>34</v>
       </c>
@@ -10594,7 +10603,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -10639,7 +10648,7 @@
       <c r="S36" s="3"/>
       <c r="T36" s="3"/>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -10686,7 +10695,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -10731,7 +10740,7 @@
       <c r="S38" s="3"/>
       <c r="T38" s="3"/>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -10778,7 +10787,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -10825,7 +10834,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20">
       <c r="A41" s="7">
         <v>40</v>
       </c>
@@ -10870,7 +10879,7 @@
       <c r="S41" s="7"/>
       <c r="T41" s="7"/>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -10913,7 +10922,7 @@
       <c r="S42" s="3"/>
       <c r="T42" s="3"/>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -10958,7 +10967,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20">
       <c r="A44" s="7">
         <v>43</v>
       </c>
@@ -11003,7 +11012,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -11050,7 +11059,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -11095,7 +11104,7 @@
       <c r="S46" s="3"/>
       <c r="T46" s="3"/>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20">
       <c r="A47" s="7">
         <v>46</v>
       </c>
@@ -11140,7 +11149,7 @@
       <c r="S47" s="7"/>
       <c r="T47" s="7"/>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -11185,7 +11194,7 @@
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -11230,7 +11239,7 @@
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -11277,7 +11286,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20">
       <c r="A51" s="33">
         <v>50</v>
       </c>
@@ -11324,7 +11333,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20">
       <c r="A52" s="3">
         <v>51</v>
       </c>
@@ -11369,7 +11378,7 @@
       <c r="S52" s="7"/>
       <c r="T52" s="7"/>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -11414,7 +11423,7 @@
       <c r="S53" s="3"/>
       <c r="T53" s="3"/>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -11459,7 +11468,7 @@
       <c r="S54" s="7"/>
       <c r="T54" s="7"/>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -11506,7 +11515,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20">
       <c r="A56" s="33">
         <v>55</v>
       </c>
@@ -11553,7 +11562,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -11600,7 +11609,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -11645,7 +11654,7 @@
       <c r="S58" s="3"/>
       <c r="T58" s="3"/>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20">
       <c r="A59" s="3">
         <v>58</v>
       </c>
@@ -11692,7 +11701,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20">
       <c r="A60" s="33">
         <v>59</v>
       </c>
@@ -11739,7 +11748,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20">
       <c r="A61" s="50">
         <v>60</v>
       </c>
@@ -11786,7 +11795,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20">
       <c r="A62" s="38">
         <v>61</v>
       </c>
@@ -11829,7 +11838,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20">
       <c r="A63" s="3">
         <v>62</v>
       </c>
@@ -11876,7 +11885,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -11921,7 +11930,7 @@
       <c r="S64" s="7"/>
       <c r="T64" s="7"/>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20">
       <c r="A65" s="3">
         <v>64</v>
       </c>
@@ -11966,7 +11975,7 @@
       <c r="S65" s="3"/>
       <c r="T65" s="3"/>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:20">
       <c r="A66" s="3">
         <v>65</v>
       </c>
@@ -12011,7 +12020,7 @@
       <c r="S66" s="3"/>
       <c r="T66" s="3"/>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:20">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -12056,7 +12065,7 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:20">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -12101,7 +12110,7 @@
       <c r="S68" s="7"/>
       <c r="T68" s="7"/>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:20">
       <c r="A69" s="3">
         <v>68</v>
       </c>
@@ -12146,7 +12155,7 @@
       <c r="S69" s="3"/>
       <c r="T69" s="3"/>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:20">
       <c r="A70" s="3">
         <v>69</v>
       </c>
@@ -12191,7 +12200,7 @@
       <c r="S70" s="3"/>
       <c r="T70" s="3"/>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20">
       <c r="A71" s="3">
         <v>70</v>
       </c>
@@ -12236,7 +12245,7 @@
       <c r="S71" s="3"/>
       <c r="T71" s="3"/>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20">
       <c r="A72" s="7">
         <v>71</v>
       </c>
@@ -12281,7 +12290,7 @@
       <c r="S72" s="3"/>
       <c r="T72" s="3"/>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20">
       <c r="A73" s="3">
         <v>72</v>
       </c>
@@ -12326,7 +12335,7 @@
       <c r="S73" s="3"/>
       <c r="T73" s="3"/>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -12371,7 +12380,7 @@
       <c r="S74" s="3"/>
       <c r="T74" s="3"/>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:20">
       <c r="A75" s="3">
         <v>74</v>
       </c>
@@ -12416,7 +12425,7 @@
       <c r="S75" s="7"/>
       <c r="T75" s="7"/>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:20">
       <c r="A76" s="28">
         <v>75</v>
       </c>
@@ -12461,7 +12470,7 @@
       <c r="S76" s="3"/>
       <c r="T76" s="3"/>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:20">
       <c r="A77" s="28">
         <v>76</v>
       </c>
@@ -12767,6 +12776,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="87796816-ee84-4612-9d42-257c84b60ab5" xsi:nil="true"/>
@@ -12775,15 +12793,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12806,6 +12815,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B8230CA-3709-4142-AC2E-55D1E2CEB32B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91756F98-8BF1-4E03-87E2-A5B630CC847C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -12814,12 +12831,4 @@
     <ds:schemaRef ds:uri="a0ba9fa7-5bf5-4390-b087-3c0a46532ba7"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B8230CA-3709-4142-AC2E-55D1E2CEB32B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>